--- a/lecture_slides/PhysHydro_CQ_toshare.xlsx
+++ b/lecture_slides/PhysHydro_CQ_toshare.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kmarkovich/Desktop/PhysHydro_Fall25/lecture_slides/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awebster2/Library/CloudStorage/Dropbox/UNM/Teaching/Guest lectures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A14F72-2479-974B-A282-F1D410C2D7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93724B0C-872F-B04F-A28B-DCE18842DECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="760" windowWidth="26660" windowHeight="17300" xr2:uid="{0166B510-342F-5946-B730-E16DA2D0F497}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="26660" windowHeight="18380" xr2:uid="{0166B510-342F-5946-B730-E16DA2D0F497}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
@@ -189,12 +189,13 @@
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="28575" cap="rnd">
                 <a:solidFill>
                   <a:srgbClr val="FF0000"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
-                <a:headEnd type="stealth"/>
+                <a:headEnd type="oval"/>
+                <a:tailEnd type="stealth" w="lg" len="lg"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -282,49 +283,49 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>2</c:v>
@@ -813,49 +814,49 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>2</c:v>
@@ -2574,7 +2575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E97028D-2B0B-5A41-9FCB-BA839254C3E9}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -2607,7 +2608,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2618,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2629,7 +2630,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2640,7 +2641,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2651,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2662,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2684,7 +2685,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2706,7 +2707,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2717,7 +2718,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2728,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2750,7 +2751,7 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2761,7 +2762,7 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2805,11 +2806,6 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C22">
         <v>1</v>
       </c>
     </row>
